--- a/Class_3_to_8_Assessment_Marks_Entry-1.xlsx
+++ b/Class_3_to_8_Assessment_Marks_Entry-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1c256028fa1a5997/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4FFA72C-9158-4D13-A15B-A2FDD415624C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F642F325-5710-4DA8-846E-1CFD3CABBE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
